--- a/SuppXLS/Scen_UC_OILBND.xlsx
+++ b/SuppXLS/Scen_UC_OILBND.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\INDIND\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0C6493-7FCE-4306-B0EC-F3E7A11141BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41995871-2313-4431-B50F-1D64DD3B49C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>Reduction Coeff</t>
-  </si>
-  <si>
-    <t>MANCO2</t>
   </si>
   <si>
     <t>Reference Scenario</t>
@@ -802,7 +799,7 @@
         <v>15</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>16</v>
@@ -816,10 +813,10 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
       </c>
       <c r="I6">
         <v>2030</v>
@@ -838,7 +835,7 @@
         <v>5</v>
       </c>
       <c r="N6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R6" s="11">
         <v>0.2</v>
@@ -846,7 +843,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I7">
         <v>2050</v>
@@ -886,12 +883,12 @@
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
@@ -934,13 +931,13 @@
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
         <v>22</v>
       </c>
-      <c r="C24" t="s">
-        <v>23</v>
-      </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
